--- a/data/rsvp-submissions.xlsx
+++ b/data/rsvp-submissions.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,18 +410,21 @@
         <v>Full Name</v>
       </c>
       <c r="D1" t="str">
+        <v>Phone Number</v>
+      </c>
+      <c r="E1" t="str">
         <v>Email</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Guests</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Children Attending</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Dietary Requirements</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Message</v>
       </c>
     </row>
@@ -448,12 +451,44 @@
         <v/>
       </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>Delete this row if you want a clean sheet.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-05-10 08:32:09 (America/Indiana/Indianapolis)</v>
+      </c>
+      <c r="B3" t="str">
+        <v>yes</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Local Test</v>
+      </c>
+      <c r="D3" t="str">
+        <v>123</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v>1</v>
+      </c>
+      <c r="G3" t="str">
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>local test</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>
 </worksheet>
 </file>